--- a/data/file_generation/input/data_75/研究二-后测共情测量原始数据导出-数字编码.xlsx
+++ b/data/file_generation/input/data_75/研究二-后测共情测量原始数据导出-数字编码.xlsx
@@ -5381,26 +5381,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{713ACB8E-4416-431B-8996-0AC155682622}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38BBBFD-C03F-4DBB-85A1-681E3F31FA48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{521A8D57-DFED-454A-AA74-E4626BDA0BC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB0C1958-D78E-448C-B5A6-B7CF915CD4F6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E911DD6-05AD-4C39-8378-03261D23274B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4B2798C-99DC-42CF-82F4-9C3B91C6AB47}"/>
 </file>